--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3360,8 +3476,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3380,933 +3500,841 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도라지 타령 — 민요채보-1/도라지 타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">도라지 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">대</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G4" s="16"/>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="16"/>
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">심</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">장</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="J6" s="13"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">뿌</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">반</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="P7" s="13"/>
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">스리</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에헤</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O8" s="17"/>
+      <c r="P8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">캐어</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="K10" s="16"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="16"/>
+      <c r="P10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">살살</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 南</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">되</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="O11" s="17"/>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="Q12" s="15"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="16"/>
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">지화</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="16"/>
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">녹인다</t>
         </is>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="D14" s="13"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="17"/>
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="M14" s="17"/>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="Q14" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3747,93 +3797,93 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">도라지 타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3841,69 +3891,69 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="26"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">심</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3911,61 +3961,61 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">뿌</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3973,67 +4023,67 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">득</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">캐</t>
         </is>
@@ -4041,62 +4091,62 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="26"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="G7" s="26"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4104,164 +4154,164 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G8" s="27"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="I8" s="28"/>
+      <c r="J8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="K8" s="30"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="O8" s="10"/>
+      <c r="O8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="I9" s="24"/>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="L9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">케</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O9" s="8"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M10" s="26"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -4269,112 +4319,112 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 林</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
+      <c r="O11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="19" t="inlineStr">
+      <c r="M12" s="22"/>
+      <c r="N12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?
 仲</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="O12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4382,96 +4432,96 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="26"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="I13" s="26"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K13" s="26"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="26"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
+      <c r="O13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="28"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
+      <c r="O14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -3776,26 +3776,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="O8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="O11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="O13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -245,6 +250,30 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3823,7 +3852,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3833,7 +3862,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -3843,7 +3872,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3853,7 +3882,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3863,7 +3892,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3873,7 +3902,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -3883,7 +3912,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3896,7 +3925,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3907,13 +3936,13 @@
 無</t>
         </is>
       </c>
-      <c r="E4" s="26"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3923,7 +3952,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3933,7 +3962,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">심</t>
         </is>
@@ -3943,7 +3972,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">두</t>
         </is>
@@ -3953,7 +3982,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O4" s="26" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3966,19 +3995,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="36"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3988,14 +4017,14 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="36"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -4005,7 +4034,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">뿌</t>
         </is>
@@ -4015,7 +4044,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -4029,13 +4058,13 @@
 無</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">득</t>
         </is>
@@ -4046,14 +4075,14 @@
 仲</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4063,7 +4092,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
@@ -4073,7 +4102,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4083,7 +4112,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">캐</t>
         </is>
@@ -4097,34 +4126,34 @@
 姑</t>
         </is>
       </c>
-      <c r="C7" s="26"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4135,7 +4164,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4146,7 +4175,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O7" s="26" t="inlineStr">
+      <c r="O7" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4159,44 +4188,44 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="36"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="36"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I8" s="28"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="K8" s="30"/>
+      <c r="K8" s="38"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="36"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="O8" s="27"/>
+      <c r="O8" s="36"/>
     </row>
     <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
@@ -4205,7 +4234,7 @@
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4215,7 +4244,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
@@ -4225,7 +4254,7 @@
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4235,13 +4264,13 @@
           <t xml:space="preserve">仲／</t>
         </is>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="33"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -4251,7 +4280,7 @@
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="M9" s="24" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">케</t>
         </is>
@@ -4262,7 +4291,7 @@
 姑</t>
         </is>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="32"/>
     </row>
     <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
@@ -4271,31 +4300,31 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="35"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="35"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4305,13 +4334,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M10" s="26"/>
+      <c r="M10" s="35"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢／</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
+      <c r="O10" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -4325,42 +4354,42 @@
 無</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="36"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="36"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 林</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4371,7 +4400,7 @@
 無</t>
         </is>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="36"/>
     </row>
     <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
@@ -4380,26 +4409,26 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -4410,21 +4439,21 @@
 潢</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="32"/>
       <c r="N12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?
 仲</t>
         </is>
       </c>
-      <c r="O12" s="31" t="inlineStr">
+      <c r="O12" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4437,46 +4466,46 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I13" s="26"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="26"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M13" s="26"/>
+      <c r="M13" s="35"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="35"/>
     </row>
     <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
@@ -4485,43 +4514,43 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="36"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="36"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="36"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="36"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -588,10 +588,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -534,17 +534,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -661,7 +661,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -703,6 +703,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3751,532 +3779,532 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:O14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="12" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="16"/>
+      <c r="N4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="17"/>
+      <c r="L5" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B10" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="O10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B11" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="17"/>
+      <c r="F11" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="17"/>
+      <c r="H11" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="17"/>
+      <c r="J11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="17"/>
+      <c r="L11" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="10" t="s">
+      <c r="M11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="17" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B13" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="16"/>
+      <c r="F13" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="16"/>
+      <c r="H13" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="16"/>
+      <c r="J13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="16"/>
+      <c r="L13" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="16"/>
+      <c r="N13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="O13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="O13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B14" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="17"/>
+      <c r="D14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="17"/>
+      <c r="H14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="17"/>
+      <c r="J14" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="17"/>
+      <c r="L14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="17"/>
+      <c r="N14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="17" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4286,7 +4314,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="86" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/도라지 타령.xlsx
+++ b/sheets/민요/검수/도라지 타령.xlsx
@@ -3785,19 +3785,19 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="12" width="6"/>
   </cols>
   <sheetData>
